--- a/XLibur.Tests/Resource/Other/StyleReferenceFiles/ConditionalFormattingOrder/ConditionalFormattingOrder.xlsx
+++ b/XLibur.Tests/Resource/Other/StyleReferenceFiles/ConditionalFormattingOrder/ConditionalFormattingOrder.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
